--- a/tabtools/qa/output/regtab_ext_test4.xlsx
+++ b/tabtools/qa/output/regtab_ext_test4.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="350" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="385" uniqueCount="17">
   <si>
     <t>Test 4: Cox Model</t>
   </si>
@@ -70,10 +70,818 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fonts count="1861">
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
+  <fonts count="2047">
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
     </font>
     <font>
       <sz val="11"/>
@@ -8164,7 +8972,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1441">
+  <borders count="1585">
     <border>
       <left/>
       <right/>
@@ -17952,11 +18760,989 @@
       <bottom style="thin"/>
       <diagonal style="none"/>
     </border>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1441">
+  <cellXfs count="1585">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0"/>
@@ -23565,6 +25351,567 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="1860" fillId="0" borderId="1440" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1441" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1442" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1443" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1444" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1445" xfId="0"/>
+    <xf numFmtId="0" fontId="1861" fillId="0" borderId="1446" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1862" fillId="0" borderId="1447" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1863" fillId="0" borderId="1448" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1864" fillId="0" borderId="1449" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1865" fillId="0" borderId="1450" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1866" fillId="0" borderId="1451" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1868" fillId="0" borderId="1452" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1870" fillId="0" borderId="1453" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1872" fillId="0" borderId="1454" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1873" fillId="0" borderId="1455" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1874" fillId="0" borderId="1456" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1875" fillId="0" borderId="1457" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1876" fillId="0" borderId="1458" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1877" fillId="0" borderId="1459" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1878" fillId="0" borderId="1460" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1879" fillId="0" borderId="1461" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1880" fillId="0" borderId="1462" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1881" fillId="0" borderId="1463" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1882" fillId="0" borderId="1464" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1883" fillId="0" borderId="1465" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1884" fillId="0" borderId="1466" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1885" fillId="0" borderId="1467" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1886" fillId="0" borderId="1468" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1887" fillId="0" borderId="1469" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1888" fillId="0" borderId="1470" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1889" fillId="0" borderId="1471" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1890" fillId="0" borderId="1472" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1891" fillId="0" borderId="1473" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1893" fillId="0" borderId="1474" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1895" fillId="0" borderId="1475" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1897" fillId="0" borderId="1476" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1899" fillId="0" borderId="1477" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1901" fillId="0" borderId="1478" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1902" fillId="0" borderId="1479" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1903" fillId="0" borderId="1480" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1904" fillId="0" borderId="1481" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1905" fillId="0" borderId="1482" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1906" fillId="0" borderId="1483" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1907" fillId="0" borderId="1484" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1908" fillId="0" borderId="1485" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1909" fillId="0" borderId="1486" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1910" fillId="0" borderId="1487" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1911" fillId="0" borderId="1488" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1912" fillId="0" borderId="1489" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1913" fillId="0" borderId="1490" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1914" fillId="0" borderId="1491" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1916" fillId="0" borderId="1492" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1918" fillId="0" borderId="1493" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1920" fillId="0" borderId="1494" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1922" fillId="0" borderId="1495" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1923" fillId="0" borderId="1496" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1924" fillId="0" borderId="1497" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1925" fillId="0" borderId="1498" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1926" fillId="0" borderId="1499" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1927" fillId="0" borderId="1500" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1928" fillId="0" borderId="1501" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1929" fillId="0" borderId="1502" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1930" fillId="0" borderId="1503" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1931" fillId="0" borderId="1504" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1932" fillId="0" borderId="1505" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1933" fillId="0" borderId="1506" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1934" fillId="0" borderId="1507" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1935" fillId="0" borderId="1508" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1936" fillId="0" borderId="1509" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1937" fillId="0" borderId="1510" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1938" fillId="0" borderId="1511" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1939" fillId="0" borderId="1512" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1940" fillId="0" borderId="1513" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1941" fillId="0" borderId="1514" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1942" fillId="0" borderId="1515" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1943" fillId="0" borderId="1516" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1944" fillId="0" borderId="1517" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1945" fillId="0" borderId="1518" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1946" fillId="0" borderId="1519" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1947" fillId="0" borderId="1520" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1948" fillId="0" borderId="1521" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1949" fillId="0" borderId="1522" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1950" fillId="0" borderId="1523" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1951" fillId="0" borderId="1524" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1952" fillId="0" borderId="1525" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1953" fillId="0" borderId="1526" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1954" fillId="0" borderId="1527" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1955" fillId="0" borderId="1528" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1956" fillId="0" borderId="1529" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1957" fillId="0" borderId="1530" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1958" fillId="0" borderId="1531" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1959" fillId="0" borderId="1532" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1960" fillId="0" borderId="1533" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1961" fillId="0" borderId="1534" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1962" fillId="0" borderId="1535" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1963" fillId="0" borderId="1536" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1964" fillId="0" borderId="1537" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1965" fillId="0" borderId="1538" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1966" fillId="0" borderId="1539" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1967" fillId="0" borderId="1540" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1968" fillId="0" borderId="1541" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1969" fillId="0" borderId="1542" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1970" fillId="0" borderId="1543" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1971" fillId="0" borderId="1544" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1972" fillId="0" borderId="1545" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1973" fillId="0" borderId="1546" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1974" fillId="0" borderId="1547" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1975" fillId="0" borderId="1548" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1976" fillId="0" borderId="1549" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1978" fillId="0" borderId="1550" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1980" fillId="0" borderId="1551" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1982" fillId="0" borderId="1552" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1984" fillId="0" borderId="1553" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1986" fillId="0" borderId="1554" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1988" fillId="0" borderId="1555" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1990" fillId="0" borderId="1556" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1992" fillId="0" borderId="1557" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1994" fillId="0" borderId="1558" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1996" fillId="0" borderId="1559" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1998" fillId="0" borderId="1560" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2000" fillId="0" borderId="1561" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2002" fillId="0" borderId="1562" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2004" fillId="0" borderId="1563" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2006" fillId="0" borderId="1564" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2008" fillId="0" borderId="1565" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2010" fillId="0" borderId="1566" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2012" fillId="0" borderId="1567" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2014" fillId="0" borderId="1568" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2016" fillId="0" borderId="1569" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2018" fillId="0" borderId="1570" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2020" fillId="0" borderId="1571" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2022" fillId="0" borderId="1572" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2024" fillId="0" borderId="1573" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2026" fillId="0" borderId="1574" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2028" fillId="0" borderId="1575" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2030" fillId="0" borderId="1576" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2032" fillId="0" borderId="1577" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2034" fillId="0" borderId="1578" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2036" fillId="0" borderId="1579" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2038" fillId="0" borderId="1580" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2040" fillId="0" borderId="1581" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2042" fillId="0" borderId="1582" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2044" fillId="0" borderId="1583" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2046" fillId="0" borderId="1584" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -23580,128 +25927,128 @@
   <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="14.7109375" style="1298" customWidth="true"/>
-    <col min="3" max="3" width="5.11328125" style="1299" customWidth="true"/>
-    <col min="4" max="4" width="11.11328125" style="1300" customWidth="true"/>
-    <col min="5" max="5" width="7.7109375" style="1301" customWidth="true"/>
+    <col min="2" max="2" width="14.7109375" style="1442" customWidth="true"/>
+    <col min="3" max="3" width="5.11328125" style="1443" customWidth="true"/>
+    <col min="4" max="4" width="11.11328125" style="1444" customWidth="true"/>
+    <col min="5" max="5" width="7.7109375" style="1445" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" s="1297" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="1406" t="s">
+    <row r="1" s="1441" customFormat="true" ht="30" customHeight="true">
+      <c r="A1" s="1550" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1407" t="s">
+      <c r="B1" s="1551" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1408" t="s">
+      <c r="C1" s="1552" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1409" t="s">
+      <c r="D1" s="1553" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="1410" t="s">
+      <c r="E1" s="1554" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1411" t="s">
+      <c r="A2" s="1555" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="1412" t="s">
+      <c r="B2" s="1556" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="1413" t="s">
+      <c r="C2" s="1557" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="1414" t="s">
+      <c r="D2" s="1558" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="1415" t="s">
+      <c r="E2" s="1559" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1416" t="s">
+      <c r="A3" s="1560" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="1417" t="s">
+      <c r="B3" s="1561" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="1418" t="s">
+      <c r="C3" s="1562" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="1419" t="s">
+      <c r="D3" s="1563" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="1420" t="s">
+      <c r="E3" s="1564" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1421" t="s">
+      <c r="A4" s="1565" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="1422" t="s">
+      <c r="B4" s="1566" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="1423" t="s">
+      <c r="C4" s="1567" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="1424" t="s">
+      <c r="D4" s="1568" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="1425" t="s">
+      <c r="E4" s="1569" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1426" t="s">
+      <c r="A5" s="1570" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="1427" t="s">
+      <c r="B5" s="1571" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="1428" t="s">
+      <c r="C5" s="1572" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="1429" t="s">
+      <c r="D5" s="1573" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="1430" t="s">
+      <c r="E5" s="1574" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1431" t="s">
+      <c r="A6" s="1575" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="1432" t="s">
+      <c r="B6" s="1576" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="1433" t="s">
+      <c r="C6" s="1577" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="1434" t="s">
+      <c r="D6" s="1578" t="s">
         <v>1</v>
       </c>
-      <c r="E6" s="1435" t="s">
+      <c r="E6" s="1579" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1436" t="s">
+      <c r="A7" s="1580" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="1437" t="s">
+      <c r="B7" s="1581" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="1438" t="s">
+      <c r="C7" s="1582" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="1439" t="s">
+      <c r="D7" s="1583" t="s">
         <v>1</v>
       </c>
-      <c r="E7" s="1440" t="s">
+      <c r="E7" s="1584" t="s">
         <v>1</v>
       </c>
     </row>
